--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-28.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-02-28.xlsx
@@ -720,18 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -742,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,18 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -786,19 +794,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -856,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1582,22 +1582,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Balance of TradeNOV</t>
+          <t>ExportsNOV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$-78.2B</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>$-78B</t>
-        </is>
-      </c>
+          <t>$273.4B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$-70B</t>
+          <t>$264B</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1612,18 +1608,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ExportsNOV</t>
+          <t>ImportsNOV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$273.4B</t>
+          <t>$351.6B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$264B</t>
+          <t>$334B</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1638,18 +1634,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ImportsNOV</t>
+          <t>Balance of TradeNOV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$351.6B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>$-78.2B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>$-78B</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>$334B</t>
+          <t>$-70B</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMDEC</t>
+          <t>Used Car Prices YoYDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYDEC</t>
+          <t>Used Car Prices MoMDEC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,26 +3174,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3204,22 +3200,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4.180%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.180%</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4070,26 +4070,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4100,22 +4096,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4126,26 +4126,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4156,26 +4156,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4186,22 +4186,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4252,22 +4252,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,18 +4296,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -4322,15 +4322,19 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>3</v>
@@ -4344,19 +4348,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4392,22 +4392,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4418,18 +4414,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,16 +4556,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4578,26 +4586,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4608,24 +4608,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4638,20 +4630,16 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
         <v>3</v>
       </c>
@@ -4664,26 +4652,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,22 +4682,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4724,18 +4712,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4746,26 +4742,22 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -4776,20 +4768,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4802,18 +4790,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4824,22 +4820,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4854,16 +4850,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,22 +4876,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -4906,16 +4906,20 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -4928,18 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4954,26 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4992,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,26 +5014,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
@@ -5240,22 +5240,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -5266,18 +5270,18 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -5292,26 +5296,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,22 +5942,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5972,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,19 +6176,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,22 +6264,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -6290,22 +6286,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6316,12 +6308,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,15 +6330,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,18 +6378,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,22 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6560,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6594,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6620,12 +6624,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,26 +6684,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6710,26 +6714,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7178,18 +7178,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,18 +7208,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7260,18 +7264,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,22 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7790,19 +7790,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
         <v>3</v>
@@ -7816,18 +7812,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7838,22 +7838,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,12 +7860,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,17 +7904,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -7934,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,15 +7974,19 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
         <v>3</v>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,22 +8100,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8122,18 +8130,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8148,22 +8160,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -8174,26 +8190,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8204,22 +8220,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8234,26 +8246,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,26 +8272,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8516,22 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -8542,24 +8546,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8572,18 +8564,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8628,22 +8624,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,26 +8654,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8680,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8718,22 +8710,18 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,22 +8736,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8778,14 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,26 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -8934,22 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8964,22 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,26 +8990,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/06</t>
+          <t>30-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>6.89%</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/06</t>
+          <t>15-Year Mortgage RateFEB/06</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -10536,22 +10536,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10566,22 +10562,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -10592,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -10652,22 +10652,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10678,26 +10682,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10712,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10742,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10768,22 +10768,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,22 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10930,22 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,18 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10986,22 +10990,18 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,22 +11016,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11564,22 +11564,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11590,22 +11586,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11616,7 +11612,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -11627,7 +11623,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11642,22 +11638,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11668,18 +11664,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11694,18 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -12002,14 +12002,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,14 +12024,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12046,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12072,18 +12068,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12098,18 +12094,22 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -12120,14 +12120,14 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12142,18 +12142,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12168,22 +12168,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12194,18 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -12360,14 +12360,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F490" t="n">
@@ -12382,14 +12382,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12430,18 +12430,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -12452,22 +12456,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12478,22 +12478,18 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12504,18 +12500,22 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12526,22 +12526,18 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12552,18 +12548,22 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12574,22 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,22 +12596,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -12626,18 +12622,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12652,14 +12648,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12696,22 +12696,22 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="505">
@@ -12722,22 +12722,22 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
@@ -13288,14 +13288,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -13306,7 +13310,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -13324,18 +13328,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13472,14 +13472,14 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
       <c r="F544" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
       <c r="F545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -13526,14 +13526,14 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -13644,18 +13644,22 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -13666,22 +13670,18 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14860,14 +14860,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14914,14 +14914,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="618">
@@ -14932,14 +14932,14 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr"/>
       <c r="F618" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="619">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -16110,7 +16110,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16596,14 +16596,14 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
       <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="703">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C703" t="inlineStr"/>
@@ -16650,14 +16650,14 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="706">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -16830,14 +16830,14 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr"/>
       <c r="F715" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="716">
@@ -16848,14 +16848,14 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
@@ -16866,14 +16866,14 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
       <c r="F717" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="718">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
@@ -17010,14 +17010,14 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr"/>
       <c r="F725" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="726">
@@ -17118,7 +17118,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17244,7 +17244,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17406,7 +17406,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
@@ -17694,12 +17694,20 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr"/>
-      <c r="E761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F761" t="n">
         <v>3</v>
       </c>
@@ -17734,22 +17742,22 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F763" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764">
@@ -17760,14 +17768,14 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -17778,20 +17786,12 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D765" t="inlineStr"/>
+      <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
         <v>3</v>
       </c>
@@ -17804,14 +17804,22 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr"/>
-      <c r="E766" t="inlineStr"/>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F766" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="767">
@@ -17822,22 +17830,14 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E767" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D767" t="inlineStr"/>
+      <c r="E767" t="inlineStr"/>
       <c r="F767" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="768">
@@ -17848,12 +17848,20 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
-      <c r="D768" t="inlineStr"/>
-      <c r="E768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F768" t="n">
         <v>3</v>
       </c>
@@ -17866,14 +17874,18 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="inlineStr"/>
-      <c r="E769" t="inlineStr"/>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F769" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="770">
@@ -17884,18 +17896,14 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr"/>
-      <c r="E770" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E770" t="inlineStr"/>
       <c r="F770" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="771">
@@ -17906,14 +17914,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="772">
@@ -17946,22 +17954,14 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
-      <c r="D773" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr"/>
       <c r="F773" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="774">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C792" t="inlineStr"/>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
